--- a/VerveStacks_IRL_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IRL_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IRL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10883DEB-31FC-4B66-9DEC-FEBEDC3C8D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D700E0DB-F1C0-4FBA-9C60-0D92FF12D269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3497" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3487" uniqueCount="604">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -1943,15 +1943,6 @@
   </si>
   <si>
     <t>STG</t>
-  </si>
-  <si>
-    <t>Trd_electricity import</t>
-  </si>
-  <si>
-    <t>e_IE11-220,e_IE6-220,e_w104388595-220,e_w104388599-220,e_w1154822210-220,e_w147525695-220,e_w207331199-220,e_w207339053-220,e_w207339053-400,e_w208124159-220,e_w255668124-220,e_w264275258-220,e_w264275258-275,e_w35150701-220,e_w361261945-220,e_w516651650-220,e_w714018181-220,e_w79803767-220</t>
-  </si>
-  <si>
-    <t>Trd_electricity export</t>
   </si>
 </sst>
 </file>
@@ -3166,10 +3157,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F018B72D-F937-4E75-B36A-73E060845420}">
-  <dimension ref="B2:AJ293"/>
+  <dimension ref="B2:AF293"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -3182,11 +3173,8 @@
       <c r="U2" t="s">
         <v>267</v>
       </c>
-      <c r="AH2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="3" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -3238,17 +3226,8 @@
       <c r="AA3" t="s">
         <v>221</v>
       </c>
-      <c r="AH3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>222</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="4" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>156</v>
       </c>
@@ -3315,17 +3294,8 @@
       <c r="AF4" t="s">
         <v>601</v>
       </c>
-      <c r="AH4" t="s">
-        <v>604</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>605</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>157</v>
       </c>
@@ -3389,17 +3359,8 @@
       <c r="AF5" t="s">
         <v>602</v>
       </c>
-      <c r="AH5" t="s">
-        <v>606</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>605</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>158</v>
       </c>
@@ -3464,7 +3425,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>159</v>
       </c>
@@ -3514,7 +3475,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>160</v>
       </c>
@@ -3564,7 +3525,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>161</v>
       </c>
@@ -3614,7 +3575,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>162</v>
       </c>
@@ -3664,7 +3625,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>163</v>
       </c>
@@ -3714,7 +3675,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>164</v>
       </c>
@@ -3764,7 +3725,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>165</v>
       </c>
@@ -3814,7 +3775,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>166</v>
       </c>
@@ -3864,7 +3825,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>167</v>
       </c>
@@ -3914,7 +3875,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>168</v>
       </c>
